--- a/astro-site/public/dl/kit-tareas/06-eventos-festivos.xlsx
+++ b/astro-site/public/dl/kit-tareas/06-eventos-festivos.xlsx
@@ -1,23 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Pre-Evento" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="San Valentín" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Navidad" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Temporada Terraza" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pre-Evento" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="San Valentín" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Navidad" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temporada Terraza" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Pre-Evento'!$A$1:$G$38</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'San Valentín'!$A$1:$G$24</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Navidad'!$A$1:$G$30</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Temporada Terraza'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Pre-Evento'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Pre-Evento'!$A$1:$G$38</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'San Valentín'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'San Valentín'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Navidad'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Navidad'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Temporada Terraza'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Temporada Terraza'!$A$1:$G$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -137,7 +141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -159,59 +163,118 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="28">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -571,15 +634,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B10"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -587,6 +651,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -594,9 +659,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -618,9 +681,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -628,8 +689,33 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -638,18 +724,18 @@
   <sheetPr>
     <tabColor rgb="00E91E63"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -666,10 +752,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -694,7 +781,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -709,18 +796,16 @@
           <t xml:space="preserve">  48 HORAS ANTES</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -746,10 +831,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -775,10 +858,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="27" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -804,10 +885,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="27" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -833,10 +912,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -862,10 +939,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="27" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -890,24 +965,23 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="15" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  24 HORAS ANTES</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
+      <c r="B13" s="25" t="n"/>
+      <c r="C13" s="25" t="n"/>
+      <c r="D13" s="25" t="n"/>
+      <c r="E13" s="25" t="n"/>
+      <c r="F13" s="25" t="n"/>
+      <c r="G13" s="26" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -933,10 +1007,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="27" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -962,10 +1034,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="27" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -991,10 +1061,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="27" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1020,10 +1088,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="27" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1048,24 +1114,23 @@
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="15" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  DÍA DEL EVENTO — MAÑANA</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
-      <c r="F20" s="17" t="n"/>
-      <c r="G20" s="17" t="n"/>
+      <c r="B20" s="25" t="n"/>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="25" t="n"/>
+      <c r="F20" s="25" t="n"/>
+      <c r="G20" s="26" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="27" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1091,10 +1156,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="27" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1120,10 +1183,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="27" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1149,10 +1210,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="27" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1178,10 +1237,8 @@
       <c r="G24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="27" t="n">
+        <v>16</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -1206,24 +1263,23 @@
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="15" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  DÍA DEL EVENTO — POST</t>
         </is>
       </c>
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="17" t="n"/>
-      <c r="G27" s="17" t="n"/>
+      <c r="B27" s="25" t="n"/>
+      <c r="C27" s="25" t="n"/>
+      <c r="D27" s="25" t="n"/>
+      <c r="E27" s="25" t="n"/>
+      <c r="F27" s="25" t="n"/>
+      <c r="G27" s="26" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="27" t="n">
+        <v>17</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -1249,10 +1305,8 @@
       <c r="G28" s="15" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="27" t="n">
+        <v>18</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -1278,10 +1332,8 @@
       <c r="G29" s="15" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A30" s="27" t="n">
+        <v>19</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -1307,10 +1359,8 @@
       <c r="G30" s="15" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A31" s="27" t="n">
+        <v>20</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
@@ -1335,6 +1385,8 @@
       <c r="F31" s="14" t="n"/>
       <c r="G31" s="15" t="n"/>
     </row>
+    <row r="32"/>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
@@ -1343,17 +1395,19 @@
       </c>
       <c r="D34" s="19">
         <f>COUNTIF(F5:F32,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F34" s="19" t="n">
-        <v>20</v>
-      </c>
-    </row>
+      <c r="F34" s="19">
+        <f>COUNTIF(B5:B32,"?*")</f>
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
@@ -1361,13 +1415,17 @@
         </is>
       </c>
       <c r="B36" s="15" t="n"/>
+      <c r="C36" s="25" t="n"/>
+      <c r="D36" s="26" t="n"/>
       <c r="E36" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F36" s="15" t="n"/>
-    </row>
+      <c r="G36" s="26" t="n"/>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="21" t="inlineStr">
         <is>
@@ -1380,20 +1438,33 @@
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F36:G36"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A34:C34"/>
-    <mergeCell ref="F36:G36"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="B36:D36"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G32">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F21 F22 F23 F24 F25 F28 F29 F30 F31" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F21 F22 F23 F24 F25 F28 F29 F30 F31 F32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1402,18 +1473,18 @@
   <sheetPr>
     <tabColor rgb="00E91E63"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1430,10 +1501,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1458,7 +1530,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1473,18 +1545,16 @@
           <t xml:space="preserve">  1 SEMANA ANTES</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1510,10 +1580,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1539,10 +1607,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="27" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1568,10 +1634,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="27" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1597,10 +1661,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1625,24 +1687,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  DÍA DE SAN VALENTÍN</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="17" t="n"/>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="26" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="27" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1668,10 +1729,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1697,10 +1756,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="27" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1726,10 +1783,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="27" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -1755,10 +1810,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="27" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1783,6 +1836,8 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
@@ -1791,17 +1846,19 @@
       </c>
       <c r="D20" s="19">
         <f>COUNTIF(F5:F18,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F20" s="19" t="n">
-        <v>10</v>
-      </c>
-    </row>
+      <c r="F20" s="19">
+        <f>COUNTIF(B5:B18,"?*")</f>
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
@@ -1809,13 +1866,17 @@
         </is>
       </c>
       <c r="B22" s="15" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="26" t="n"/>
       <c r="E22" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F22" s="15" t="n"/>
-    </row>
+      <c r="G22" s="26" t="n"/>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="21" t="inlineStr">
         <is>
@@ -1833,13 +1894,26 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="F22:G22"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G18">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1848,18 +1922,18 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1876,10 +1950,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1904,7 +1979,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1919,18 +1994,16 @@
           <t xml:space="preserve">  2 SEMANAS ANTES</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1956,10 +2029,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1985,10 +2056,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="27" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -2014,10 +2083,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="27" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -2043,10 +2110,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -2071,24 +2136,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  SEMANA DE NAVIDAD</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="17" t="n"/>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="26" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="27" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -2114,10 +2178,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -2143,10 +2205,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="27" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -2172,10 +2232,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="27" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2201,10 +2259,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="27" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2229,24 +2285,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOCHEVIEJA</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="17" t="n"/>
-      <c r="G19" s="17" t="n"/>
+      <c r="B19" s="25" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
+      <c r="G19" s="26" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="27" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -2272,10 +2327,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="27" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -2301,10 +2354,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="27" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -2330,10 +2381,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="27" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -2358,6 +2407,8 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="15" t="n"/>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
@@ -2366,17 +2417,19 @@
       </c>
       <c r="D26" s="19">
         <f>COUNTIF(F5:F24,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F26" s="19" t="n">
-        <v>14</v>
-      </c>
-    </row>
+      <c r="F26" s="19">
+        <f>COUNTIF(B5:B24,"?*")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
@@ -2384,13 +2437,17 @@
         </is>
       </c>
       <c r="B28" s="15" t="n"/>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="26" t="n"/>
       <c r="E28" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F28" s="15" t="n"/>
-    </row>
+      <c r="G28" s="26" t="n"/>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
         <is>
@@ -2409,13 +2466,26 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B28:D28"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G24">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2424,18 +2494,18 @@
   <sheetPr>
     <tabColor rgb="00FF9800"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2452,10 +2522,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2480,7 +2551,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2495,18 +2566,16 @@
           <t xml:space="preserve">  APERTURA DE TEMPORADA</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
-      <c r="E5" s="23" t="n"/>
-      <c r="F5" s="23" t="n"/>
-      <c r="G5" s="23" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -2532,10 +2601,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -2561,10 +2628,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="27" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -2590,10 +2655,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="27" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -2619,10 +2682,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -2648,10 +2709,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="27" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -2676,24 +2735,23 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="15" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE DE TEMPORADA</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="23" t="n"/>
-      <c r="F13" s="23" t="n"/>
-      <c r="G13" s="23" t="n"/>
+      <c r="B13" s="25" t="n"/>
+      <c r="C13" s="25" t="n"/>
+      <c r="D13" s="25" t="n"/>
+      <c r="E13" s="25" t="n"/>
+      <c r="F13" s="25" t="n"/>
+      <c r="G13" s="26" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -2719,10 +2777,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="27" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -2748,10 +2804,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="27" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2777,10 +2831,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="27" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2806,10 +2858,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="27" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -2834,6 +2884,8 @@
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="15" t="n"/>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
@@ -2842,17 +2894,19 @@
       </c>
       <c r="D21" s="19">
         <f>COUNTIF(F5:F19,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F21" s="19" t="n">
-        <v>11</v>
-      </c>
-    </row>
+      <c r="F21" s="19">
+        <f>COUNTIF(B5:B19,"?*")</f>
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
@@ -2860,13 +2914,17 @@
         </is>
       </c>
       <c r="B23" s="15" t="n"/>
+      <c r="C23" s="25" t="n"/>
+      <c r="D23" s="26" t="n"/>
       <c r="E23" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F23" s="15" t="n"/>
-    </row>
+      <c r="G23" s="26" t="n"/>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="21" t="inlineStr">
         <is>
@@ -2884,12 +2942,25 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B23:D23"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G19">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas/06-eventos-festivos.xlsx
+++ b/astro-site/public/dl/kit-tareas/06-eventos-festivos.xlsx
@@ -14,14 +14,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temporada Terraza" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Pre-Evento'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Pre-Evento'!$A$1:$G$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Pre-Evento'!$A$1:$G$49</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'San Valentín'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'San Valentín'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'San Valentín'!$A$1:$G$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Navidad'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Navidad'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Navidad'!$A$1:$G$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Temporada Terraza'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Temporada Terraza'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Temporada Terraza'!$A$1:$G$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -102,8 +103,22 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -138,6 +153,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F3E5F5"/>
         <bgColor rgb="00F3E5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -211,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -259,6 +279,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -636,72 +717,190 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>Tareas para Eventos y Festivos — Restaurante Casual</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Cómo usar estas plantillas</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>▸ Usa la pestaña Pre-Evento para planificar cualquier evento</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>▸ Las pestañas de festivos son para fechas señaladas del año</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="3" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>▸ Personaliza con las tradiciones y menú de tu restaurante</t>
         </is>
       </c>
     </row>
     <row r="9"/>
-    <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes · AI Chef Pro · aichef.pro</t>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="29" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día (accesos, luces, clima, terraza).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala, barra).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. No se duplican: cada uno cubre un nivel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>▸ Estás en 06-eventos-festivos.xlsx: lo excepcional (eventos, festivos, temporada). El día a día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="29" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="35" customHeight="1">
+      <c r="B36" s="29" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="29" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="29" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -726,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -741,14 +940,14 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Checklist Pre-Evento (48h → Día del Evento)</t>
+          <t>Checklist Pre-Evento (de la reserva al día del evento)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Evento / temporada: ___________________    Fecha: ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -776,7 +975,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Antelación</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -791,667 +990,894 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AL CONFIRMAR LA RESERVA</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="33" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Recoger POR ESCRITO alérgenos, intolerancias y dietas especiales de los comensales y trasladarlos a cocina</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="37" t="inlineStr">
+        <is>
+          <t>Al confirmar</t>
+        </is>
+      </c>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="39" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Cerrar por escrito el precio por comensal y qué incluye (bebida, café, tarta, extras)</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="37" t="inlineStr">
+        <is>
+          <t>Al confirmar</t>
+        </is>
+      </c>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="39" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Cobrar la señal o anticipo y dejar constancia del importe y la fecha</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>Al confirmar</t>
+        </is>
+      </c>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="39" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Firmar la política de cancelación y el plazo para dar el número final de comensales</t>
+        </is>
+      </c>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>Al confirmar</t>
+        </is>
+      </c>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="39" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>Acordar horario de entrada y salida del espacio y quién monta y desmonta</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>Al confirmar</t>
+        </is>
+      </c>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="39" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="n"/>
+      <c r="B11" s="40" t="n"/>
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="40" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  48 HORAS ANTES</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="26" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="33" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Confirmar número definitivo de comensales</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>48h antes</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="39" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Confirmar menú con cliente (si es privado)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>48h antes</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="39" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Verificar stock de ingredientes para el menú</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>48h antes</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="39" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Hacer pedidos extra a proveedores</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>48h antes</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="39" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>Confirmar personal extra si es necesario</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>48h antes</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="39" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>Preparar decoración especial si aplica</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D18" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E18" s="37" t="inlineStr">
         <is>
           <t>48h antes</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="F18" s="38" t="n"/>
+      <c r="G18" s="39" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="40" t="n"/>
+      <c r="B19" s="40" t="n"/>
+      <c r="C19" s="40" t="n"/>
+      <c r="D19" s="40" t="n"/>
+      <c r="E19" s="40" t="n"/>
+      <c r="F19" s="40" t="n"/>
+      <c r="G19" s="40" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  24 HORAS ANTES</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n"/>
-      <c r="C13" s="25" t="n"/>
-      <c r="D13" s="25" t="n"/>
-      <c r="E13" s="25" t="n"/>
-      <c r="F13" s="25" t="n"/>
-      <c r="G13" s="26" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B20" s="32" t="n"/>
+      <c r="C20" s="32" t="n"/>
+      <c r="D20" s="32" t="n"/>
+      <c r="E20" s="32" t="n"/>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="33" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Recibir y verificar pedidos extra</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C21" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D21" s="37" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E21" s="37" t="inlineStr">
         <is>
           <t>24h antes</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="39" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>Iniciar pre-elaboraciones que lo permitan</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C22" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D22" s="37" t="inlineStr">
         <is>
           <t>Equipo cocina</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E22" s="37" t="inlineStr">
         <is>
           <t>24h antes</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="F22" s="38" t="n"/>
+      <c r="G22" s="39" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="34" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Confirmar asignación de mesas y disposición sala</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C23" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D23" s="37" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E23" s="37" t="inlineStr">
         <is>
           <t>24h antes</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="F23" s="38" t="n"/>
+      <c r="G23" s="39" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="34" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>Briefing especial con todo el equipo</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D24" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E24" s="37" t="inlineStr">
         <is>
           <t>24h antes</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="F24" s="38" t="n"/>
+      <c r="G24" s="39" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="34" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>Verificar vajilla y cristalería suficiente</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D25" s="37" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E25" s="37" t="inlineStr">
         <is>
           <t>24h antes</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15" t="n"/>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="F25" s="38" t="n"/>
+      <c r="G25" s="39" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="40" t="n"/>
+      <c r="B26" s="40" t="n"/>
+      <c r="C26" s="40" t="n"/>
+      <c r="D26" s="40" t="n"/>
+      <c r="E26" s="40" t="n"/>
+      <c r="F26" s="40" t="n"/>
+      <c r="G26" s="40" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  DÍA DEL EVENTO — MAÑANA</t>
         </is>
       </c>
-      <c r="B20" s="25" t="n"/>
-      <c r="C20" s="25" t="n"/>
-      <c r="D20" s="25" t="n"/>
-      <c r="E20" s="25" t="n"/>
-      <c r="F20" s="25" t="n"/>
-      <c r="G20" s="26" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="27" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B27" s="32" t="n"/>
+      <c r="C27" s="32" t="n"/>
+      <c r="D27" s="32" t="n"/>
+      <c r="E27" s="32" t="n"/>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="33" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="34" t="n">
+        <v>17</v>
+      </c>
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>Montaje especial de sala según plano</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C28" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D28" s="37" t="inlineStr">
         <is>
           <t>Camareros</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E28" s="37" t="inlineStr">
         <is>
           <t>Mañana</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="27" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="F28" s="38" t="n"/>
+      <c r="G28" s="39" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>Verificar decoración, flores, velas si aplica</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D29" s="37" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E29" s="37" t="inlineStr">
         <is>
           <t>Mañana</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="27" t="n">
-        <v>14</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="F29" s="38" t="n"/>
+      <c r="G29" s="39" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="n">
+        <v>19</v>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>Mise en place completa para el evento</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D30" s="37" t="inlineStr">
         <is>
           <t>Equipo cocina</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E30" s="37" t="inlineStr">
         <is>
           <t>Mañana</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="F30" s="38" t="n"/>
+      <c r="G30" s="39" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>Test de sonido si hay música/discurso</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D31" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E31" s="37" t="inlineStr">
         <is>
           <t>Mañana</t>
         </is>
       </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="27" t="n">
-        <v>16</v>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="F31" s="38" t="n"/>
+      <c r="G31" s="39" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="34" t="n">
+        <v>21</v>
+      </c>
+      <c r="B32" s="35" t="inlineStr">
         <is>
           <t>Briefing final 30 min antes del evento</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C32" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D32" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E32" s="37" t="inlineStr">
         <is>
           <t>30 min antes</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="15" t="n"/>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="F32" s="38" t="n"/>
+      <c r="G32" s="39" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="40" t="n"/>
+      <c r="B33" s="40" t="n"/>
+      <c r="C33" s="40" t="n"/>
+      <c r="D33" s="40" t="n"/>
+      <c r="E33" s="40" t="n"/>
+      <c r="F33" s="40" t="n"/>
+      <c r="G33" s="40" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  DÍA DEL EVENTO — POST</t>
         </is>
       </c>
-      <c r="B27" s="25" t="n"/>
-      <c r="C27" s="25" t="n"/>
-      <c r="D27" s="25" t="n"/>
-      <c r="E27" s="25" t="n"/>
-      <c r="F27" s="25" t="n"/>
-      <c r="G27" s="26" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="27" t="n">
-        <v>17</v>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B34" s="32" t="n"/>
+      <c r="C34" s="32" t="n"/>
+      <c r="D34" s="32" t="n"/>
+      <c r="E34" s="32" t="n"/>
+      <c r="F34" s="32" t="n"/>
+      <c r="G34" s="33" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="34" t="n">
+        <v>22</v>
+      </c>
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>Desmontaje de sala al terminar</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C35" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D35" s="37" t="inlineStr">
         <is>
           <t>Camareros</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E35" s="37" t="inlineStr">
         <is>
           <t>Post-evento</t>
         </is>
       </c>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="15" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="27" t="n">
-        <v>18</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="F35" s="38" t="n"/>
+      <c r="G35" s="39" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="34" t="n">
+        <v>23</v>
+      </c>
+      <c r="B36" s="35" t="inlineStr">
         <is>
           <t>Limpieza profunda extra</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C36" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D36" s="37" t="inlineStr">
         <is>
           <t>Todo el equipo</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E36" s="37" t="inlineStr">
         <is>
           <t>Post-evento</t>
         </is>
       </c>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="15" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="27" t="n">
-        <v>19</v>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="F36" s="38" t="n"/>
+      <c r="G36" s="39" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="34" t="n">
+        <v>24</v>
+      </c>
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>Evaluación del evento con equipo</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C37" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D37" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E37" s="37" t="inlineStr">
         <is>
           <t>Post-evento</t>
         </is>
       </c>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="15" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="F37" s="38" t="n"/>
+      <c r="G37" s="39" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="34" t="n">
+        <v>25</v>
+      </c>
+      <c r="B38" s="35" t="inlineStr">
         <is>
           <t>Enviar agradecimiento al cliente (email/mensaje)</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C38" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D38" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E38" s="37" t="inlineStr">
         <is>
           <t>Día siguiente</t>
         </is>
       </c>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="15" t="n"/>
-    </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="F38" s="38" t="n"/>
+      <c r="G38" s="39" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="n"/>
+      <c r="B39" s="43" t="n"/>
+      <c r="C39" s="36" t="n"/>
+      <c r="D39" s="37" t="n"/>
+      <c r="E39" s="37" t="n"/>
+      <c r="F39" s="38" t="n"/>
+      <c r="G39" s="39" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="42" t="n"/>
+      <c r="B40" s="43" t="n"/>
+      <c r="C40" s="36" t="n"/>
+      <c r="D40" s="37" t="n"/>
+      <c r="E40" s="37" t="n"/>
+      <c r="F40" s="38" t="n"/>
+      <c r="G40" s="39" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="42" t="n"/>
+      <c r="B41" s="43" t="n"/>
+      <c r="C41" s="36" t="n"/>
+      <c r="D41" s="37" t="n"/>
+      <c r="E41" s="37" t="n"/>
+      <c r="F41" s="38" t="n"/>
+      <c r="G41" s="39" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="42" t="n"/>
+      <c r="B42" s="43" t="n"/>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="37" t="n"/>
+      <c r="E42" s="37" t="n"/>
+      <c r="F42" s="38" t="n"/>
+      <c r="G42" s="39" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="42" t="n"/>
+      <c r="B43" s="43" t="n"/>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="37" t="n"/>
+      <c r="E43" s="37" t="n"/>
+      <c r="F43" s="38" t="n"/>
+      <c r="G43" s="39" t="n"/>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D34" s="19">
-        <f>COUNTIF(F5:F32,"✓")</f>
+      <c r="D45" s="19">
+        <f>COUNTIFS(B5:B43,"?*",F5:F43,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="E45" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F34" s="19">
-        <f>COUNTIF(B5:B32,"?*")</f>
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="F45" s="19">
+        <f>COUNTIF(B5:B43,"?*")-COUNTIF(F5:F43,"N/A")</f>
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="25" t="n"/>
-      <c r="D36" s="26" t="n"/>
-      <c r="E36" s="19" t="inlineStr">
+      <c r="B47" s="44" t="n"/>
+      <c r="C47" s="25" t="n"/>
+      <c r="D47" s="26" t="n"/>
+      <c r="E47" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="26" t="n"/>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="F47" s="44" t="n"/>
+      <c r="G47" s="26" t="n"/>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="10">
     <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A27:G27"/>
-    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="A34:G34"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="B47:D47"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="A45:C45"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G32">
+  <conditionalFormatting sqref="A5:G43">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F21 F22 F23 F24 F25 F28 F29 F30 F31 F32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F25 F28 F29 F30 F31 F32 F35 F36 F37 F38 F39 F40 F41 F42 F43" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1475,7 +1901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1497,7 +1923,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Evento / temporada: ___________________    Fecha: ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1951,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Antelación</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1540,367 +1966,420 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  1 SEMANA ANTES</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="26" t="n"/>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Diseñar menú especial de San Valentín</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>7 días antes</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Publicar menú en redes sociales y web</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>7 días antes</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Abrir reservas con sistema de prepago o confirmación</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>7 días antes</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Comprar decoración temática (flores, pétalos, velas)</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>5 días antes</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Planificar turnos reforzados</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>5 días antes</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="39" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="n"/>
+      <c r="B11" s="40" t="n"/>
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="40" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  DÍA DE SAN VALENTÍN</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="26" t="n"/>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="33" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Decorar sala con ambientación romántica</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Camareros</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>Mañana</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="39" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Preparar detalle de bienvenida por mesa (rosa, bombón)</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>Mañana</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="39" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Preparar cocktail de bienvenida si está en menú</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>Pre-servicio</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="39" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Servicio especial: ritmo pausado, atención premium</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>Todo equipo sala</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="39" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="n">
+      <c r="A17" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>Ofrecer postre con presentación especial</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>Pastelero</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18"/>
-    <row r="19"/>
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="39" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="42" t="n"/>
+      <c r="B18" s="43" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="38" t="n"/>
+      <c r="G18" s="39" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="n"/>
+      <c r="B19" s="43" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="39" t="n"/>
+    </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D20" s="19">
-        <f>COUNTIF(F5:F18,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F20" s="19">
-        <f>COUNTIF(B5:B18,"?*")</f>
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="21"/>
+      <c r="A20" s="42" t="n"/>
+      <c r="B20" s="43" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="39" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="n"/>
+      <c r="B21" s="43" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="37" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="39" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="25" t="n"/>
-      <c r="D22" s="26" t="n"/>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="26" t="n"/>
+      <c r="A22" s="42" t="n"/>
+      <c r="B22" s="43" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="38" t="n"/>
+      <c r="G22" s="39" t="n"/>
     </row>
     <row r="23"/>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D24" s="19">
+        <f>COUNTIFS(B5:B22,"?*",F5:F22,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F24" s="19">
+        <f>COUNTIF(B5:B22,"?*")-COUNTIF(F5:F22,"N/A")</f>
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B26" s="44" t="n"/>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="26" t="n"/>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F26" s="44" t="n"/>
+      <c r="G26" s="26" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="7">
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F26:G26"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G18">
+  <conditionalFormatting sqref="A5:G22">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1924,7 +2403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1946,7 +2425,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Evento / temporada: ___________________    Fecha: ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1974,7 +2453,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Antelación</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1989,490 +2468,551 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2 SEMANAS ANTES</t>
-        </is>
-      </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="26" t="n"/>
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2-3 SEMANAS ANTES</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Diseñar menú navideño / menú de Nochevieja</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>15 días antes</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Publicar menú y abrir reservas</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>15 días antes</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Hacer pedidos especiales (marisco, cordero, turrón)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>10 días antes</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Planificar turnos de todo el periodo festivo</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>10 días antes</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Comprar decoración navideña</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>10 días antes</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="39" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="n"/>
+      <c r="B11" s="40" t="n"/>
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="40" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  SEMANA DE NAVIDAD</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="26" t="n"/>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="33" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Montar decoración navideña en sala y barra</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Camareros</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="39" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Verificar stock para toda la semana (sin entregas)</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="39" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Pre-elaboraciones extra para los días de más volumen</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Equipo cocina</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>Martes-Miérc</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="39" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Briefing especial: servicio premium, sin prisas</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>Cada día</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="39" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="n">
+      <c r="A17" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>Stock extra de cava/champagne para Nochevieja</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>30 diciembre</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18"/>
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="39" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="n"/>
+      <c r="B18" s="40" t="n"/>
+      <c r="C18" s="40" t="n"/>
+      <c r="D18" s="40" t="n"/>
+      <c r="E18" s="40" t="n"/>
+      <c r="F18" s="40" t="n"/>
+      <c r="G18" s="40" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOCHEVIEJA</t>
         </is>
       </c>
-      <c r="B19" s="25" t="n"/>
-      <c r="C19" s="25" t="n"/>
-      <c r="D19" s="25" t="n"/>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="25" t="n"/>
-      <c r="G19" s="26" t="n"/>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="32" t="n"/>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="33" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n">
+      <c r="A20" s="34" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Mise en place completa antes de las 18:00</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="37" t="inlineStr">
         <is>
           <t>Equipo cocina</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="37" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="39" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="n">
+      <c r="A21" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Decorar para la noche: cotillón, uvas, elementos especiales</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="37" t="inlineStr">
         <is>
           <t>Camareros</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="37" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="39" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="n">
+      <c r="A22" s="34" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>Preparar uvas y cava para las campanadas</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="37" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="37" t="inlineStr">
         <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="F22" s="38" t="n"/>
+      <c r="G22" s="39" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="n">
+      <c r="A23" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Servir copa de cava a todos los clientes a medianoche</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="36" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="37" t="inlineStr">
         <is>
           <t>Todo equipo</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="37" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
-    </row>
-    <row r="24"/>
-    <row r="25"/>
+      <c r="F23" s="38" t="n"/>
+      <c r="G23" s="39" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="n"/>
+      <c r="B24" s="43" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="37" t="n"/>
+      <c r="E24" s="37" t="n"/>
+      <c r="F24" s="38" t="n"/>
+      <c r="G24" s="39" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="42" t="n"/>
+      <c r="B25" s="43" t="n"/>
+      <c r="C25" s="36" t="n"/>
+      <c r="D25" s="37" t="n"/>
+      <c r="E25" s="37" t="n"/>
+      <c r="F25" s="38" t="n"/>
+      <c r="G25" s="39" t="n"/>
+    </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D26" s="19">
-        <f>COUNTIF(F5:F24,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F26" s="19">
-        <f>COUNTIF(B5:B24,"?*")</f>
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="27"/>
+      <c r="A26" s="42" t="n"/>
+      <c r="B26" s="43" t="n"/>
+      <c r="C26" s="36" t="n"/>
+      <c r="D26" s="37" t="n"/>
+      <c r="E26" s="37" t="n"/>
+      <c r="F26" s="38" t="n"/>
+      <c r="G26" s="39" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="42" t="n"/>
+      <c r="B27" s="43" t="n"/>
+      <c r="C27" s="36" t="n"/>
+      <c r="D27" s="37" t="n"/>
+      <c r="E27" s="37" t="n"/>
+      <c r="F27" s="38" t="n"/>
+      <c r="G27" s="39" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="25" t="n"/>
-      <c r="D28" s="26" t="n"/>
-      <c r="E28" s="19" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="26" t="n"/>
+      <c r="A28" s="42" t="n"/>
+      <c r="B28" s="43" t="n"/>
+      <c r="C28" s="36" t="n"/>
+      <c r="D28" s="37" t="n"/>
+      <c r="E28" s="37" t="n"/>
+      <c r="F28" s="38" t="n"/>
+      <c r="G28" s="39" t="n"/>
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D30" s="19">
+        <f>COUNTIFS(B5:B28,"?*",F5:F28,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F30" s="19">
+        <f>COUNTIF(B5:B28,"?*")-COUNTIF(F5:F28,"N/A")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B32" s="44" t="n"/>
+      <c r="C32" s="25" t="n"/>
+      <c r="D32" s="26" t="n"/>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F32" s="44" t="n"/>
+      <c r="G32" s="26" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
+    <mergeCell ref="F32:G32"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A19:G19"/>
-    <mergeCell ref="F28:G28"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="B28:D28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G24">
+  <conditionalFormatting sqref="A5:G28">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2496,7 +3036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2518,7 +3058,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Evento / temporada: ___________________    Fecha: ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -2546,7 +3086,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Antelación</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -2561,394 +3101,447 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">  APERTURA DE TEMPORADA</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="26" t="n"/>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Solicitar licencia de terraza al Ayuntamiento si aplica</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>Terraza</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="37" t="inlineStr">
+        <is>
+          <t>1 mes antes</t>
+        </is>
+      </c>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="39" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Verificar estado de mesas y sillas: reparar/sustituir</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>Terraza</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="37" t="inlineStr">
+        <is>
+          <t>1 semana antes</t>
+        </is>
+      </c>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="39" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Verificar toldo/sombrilla: estado y funcionamiento</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>Terraza</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>1 semana antes</t>
+        </is>
+      </c>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="39" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Preparar carta de terraza si es diferente</t>
+        </is>
+      </c>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>Terraza</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
+        <is>
+          <t>Jefe Cocina</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>1 semana antes</t>
+        </is>
+      </c>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="39" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Limpiar a fondo todo el mobiliario de terraza</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>Camareros</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>Día apertura</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Verificar estado de mesas y sillas: reparar/sustituir</t>
-        </is>
-      </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="39" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Verificar iluminación exterior</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>1 semana antes</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Verificar toldo/sombrilla: estado y funcionamiento</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
+        <is>
+          <t>Día apertura</t>
+        </is>
+      </c>
+      <c r="F11" s="38" t="n"/>
+      <c r="G11" s="39" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="40" t="n"/>
+      <c r="B12" s="40" t="n"/>
+      <c r="C12" s="40" t="n"/>
+      <c r="D12" s="40" t="n"/>
+      <c r="E12" s="40" t="n"/>
+      <c r="F12" s="40" t="n"/>
+      <c r="G12" s="40" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CIERRE DE TEMPORADA</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="n"/>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="32" t="n"/>
+      <c r="E13" s="32" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="33" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>Limpiar a fondo mobiliario antes de guardar</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
+        <is>
+          <t>Camareros</t>
+        </is>
+      </c>
+      <c r="E14" s="37" t="inlineStr">
+        <is>
+          <t>Último día</t>
+        </is>
+      </c>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="39" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>Guardar mobiliario en almacén</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>Terraza</t>
+        </is>
+      </c>
+      <c r="D15" s="37" t="inlineStr">
+        <is>
+          <t>Camareros</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="inlineStr">
+        <is>
+          <t>Último día</t>
+        </is>
+      </c>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="39" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Guardar sombrillas/toldos protegidos</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>Terraza</t>
+        </is>
+      </c>
+      <c r="D16" s="37" t="inlineStr">
+        <is>
+          <t>Camareros</t>
+        </is>
+      </c>
+      <c r="E16" s="37" t="inlineStr">
+        <is>
+          <t>Último día</t>
+        </is>
+      </c>
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="39" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Desmontar y guardar los calefactores exteriores si la terraza no opera en invierno</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="inlineStr">
+        <is>
+          <t>Terraza</t>
+        </is>
+      </c>
+      <c r="D17" s="37" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="E17" s="37" t="inlineStr">
+        <is>
+          <t>Último día</t>
+        </is>
+      </c>
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="39" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>Inventario de mobiliario: anotar roturas/reposiciones</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="inlineStr">
+        <is>
+          <t>Terraza</t>
+        </is>
+      </c>
+      <c r="D18" s="37" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>1 semana antes</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Solicitar licencia de terraza al Ayuntamiento si aplica</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>Terraza</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>1 mes antes</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Preparar carta de terraza si es diferente</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>Terraza</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Jefe Cocina</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>1 semana antes</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Verificar iluminación exterior</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>Terraza</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>Día apertura</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CIERRE DE TEMPORADA</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="n"/>
-      <c r="C13" s="25" t="n"/>
-      <c r="D13" s="25" t="n"/>
-      <c r="E13" s="25" t="n"/>
-      <c r="F13" s="25" t="n"/>
-      <c r="G13" s="26" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Limpiar a fondo mobiliario antes de guardar</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>Terraza</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Camareros</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E18" s="37" t="inlineStr">
         <is>
           <t>Último día</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Guardar mobiliario en almacén</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>Terraza</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Camareros</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>Último día</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Guardar sombrillas/toldos protegidos</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>Terraza</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Camareros</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>Último día</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Desmontar calefactores exteriores si aplica</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>Terraza</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Técnico</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>Último día</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Inventario de mobiliario: anotar roturas/reposiciones</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>Terraza</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>Último día</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15" t="n"/>
-    </row>
-    <row r="19"/>
-    <row r="20"/>
+      <c r="F18" s="38" t="n"/>
+      <c r="G18" s="39" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="n"/>
+      <c r="B19" s="43" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="39" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="n"/>
+      <c r="B20" s="43" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="39" t="n"/>
+    </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D21" s="19">
-        <f>COUNTIF(F5:F19,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F21" s="19">
-        <f>COUNTIF(B5:B19,"?*")</f>
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="22"/>
+      <c r="A21" s="42" t="n"/>
+      <c r="B21" s="43" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="37" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="39" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="n"/>
+      <c r="B22" s="43" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="38" t="n"/>
+      <c r="G22" s="39" t="n"/>
+    </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="25" t="n"/>
-      <c r="D23" s="26" t="n"/>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="26" t="n"/>
+      <c r="A23" s="42" t="n"/>
+      <c r="B23" s="43" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="37" t="n"/>
+      <c r="F23" s="38" t="n"/>
+      <c r="G23" s="39" t="n"/>
     </row>
     <row r="24"/>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D25" s="19">
+        <f>COUNTIFS(B5:B23,"?*",F5:F23,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F25" s="19">
+        <f>COUNTIF(B5:B23,"?*")-COUNTIF(F5:F23,"N/A")</f>
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B27" s="44" t="n"/>
+      <c r="C27" s="25" t="n"/>
+      <c r="D27" s="26" t="n"/>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F27" s="44" t="n"/>
+      <c r="G27" s="26" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="7">
+    <mergeCell ref="F27:G27"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="B23:D23"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G19">
+  <conditionalFormatting sqref="A5:G23">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/astro-site/public/dl/kit-tareas/06-eventos-festivos.xlsx
+++ b/astro-site/public/dl/kit-tareas/06-eventos-festivos.xlsx
@@ -792,6 +792,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="29" t="inlineStr">
         <is>
@@ -799,6 +800,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="32" customHeight="1">
       <c r="B18" s="30" t="inlineStr">
         <is>
@@ -813,6 +815,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="29" t="inlineStr">
         <is>
@@ -820,6 +823,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="32" customHeight="1">
       <c r="B23" s="30" t="inlineStr">
         <is>
@@ -834,6 +838,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="29" t="inlineStr">
         <is>
@@ -841,10 +846,11 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
+    <row r="27"/>
+    <row r="28" ht="16" customHeight="1">
       <c r="B28" s="30" t="inlineStr">
         <is>
-          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día (accesos, luces, clima, terraza).</t>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
         </is>
       </c>
     </row>
@@ -862,10 +868,10 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1">
+    <row r="31" ht="48" customHeight="1">
       <c r="B31" s="30" t="inlineStr">
         <is>
-          <t>▸ Orden de uso: local → áreas → caja. No se duplican: cada uno cubre un nivel.</t>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
         </is>
       </c>
     </row>
@@ -876,6 +882,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="29" t="inlineStr">
         <is>
@@ -883,6 +890,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36" ht="35" customHeight="1">
       <c r="B36" s="29" t="inlineStr">
         <is>
@@ -897,6 +905,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="29" t="inlineStr">
         <is>
@@ -1868,8 +1877,8 @@
     <mergeCell ref="A34:G34"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="B47:D47"/>
+    <mergeCell ref="A45:C45"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A45:C45"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G43">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -1877,7 +1886,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F25 F28 F29 F30 F31 F32 F35 F36 F37 F38 F39 F40 F41 F42 F43" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F25 F28 F29 F30 F31 F32 F35 F36 F37 F38 F39 F40 F41 F42 F43" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2379,7 +2388,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2997,8 +3006,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="F32:G32"/>
-    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="A2:G2"/>
@@ -3012,7 +3021,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3529,8 +3538,8 @@
   <mergeCells count="7">
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="A13:G13"/>
-    <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A5:G5"/>
@@ -3541,7 +3550,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
